--- a/stories/arbres/ATOM-SEC.ADU.002-07.xlsx
+++ b/stories/arbres/ATOM-SEC.ADU.002-07.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -602,7 +602,6 @@
           <t>secondary_lessons</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -819,6 +818,18 @@
       <c r="B29" t="inlineStr">
         <is>
           <t>xlsx-arbre-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>voice_cast</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>voix-roles-v1</t>
         </is>
       </c>
     </row>
@@ -833,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV6"/>
+  <dimension ref="A1:AW6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1127,6 +1138,11 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1151,7 +1167,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Hadrien va au marché aux fleurs. Maman vient avec lui. Maman est l'accompagnant. Hadrien aime rester avec l'accompagnant. Il marche à côté de maman. Ses pieds restent près des pieds de maman. Maman tient sa main. Les mains restent dans la main de maman. Ils voient des tulipes. Hadrien reste près. Maman dit : tu restes avec moi. Hadrien hoche la tête. Il sent la main de maman. La main est chaude. Ils sentent les roses. Hadrien reste avec maman. L'adulte connu est là. Hadrien est calme. Il sourit. Maman prend un bouquet. Hadrien reste à côté. Rester avec l'accompagnant, c'est rester près de maman. Les pieds restent près. Les mains restent tenues.</t>
+          <t>Hadrien va au marché aux fleurs. Maman vient avec lui. Maman est l'accompagnant. Hadrien aime rester avec l'accompagnant. Il marche à côté de maman. Ses pieds restent près des pieds de maman. Maman tient sa main. Les mains restent dans la main de maman. Ils voient des tulipes. Hadrien reste près. Tu restes avec moi. Hadrien hoche la tête. Il sent la main de maman. La main est chaude. Ils sentent les roses. Hadrien reste avec maman. L'adulte connu est là. Hadrien est calme. Il sourit. Maman prend un bouquet. Hadrien reste à côté. Rester avec l'accompagnant, c'est rester près de maman. Les pieds restent près. Les mains restent tenues.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1289,6 +1305,13 @@
         <v>8</v>
       </c>
       <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>narrateur|Hadrien va au marché aux fleurs. Maman vient avec lui. Maman est l'accompagnant. Hadrien aime rester avec l'accompagnant. Il marche à côté de maman. Ses pieds restent près des pieds de maman. Maman tient sa main. Les mains restent dans la main de maman. Ils voient des tulipes. Hadrien reste près.
+maman|Tu restes avec moi.
+narrateur|Hadrien hoche la tête. Il sent la main de maman. La main est chaude. Ils sentent les roses. Hadrien reste avec maman. L'adulte connu est là. Hadrien est calme. Il sourit. Maman prend un bouquet. Hadrien reste à côté. Rester avec l'accompagnant, c'est rester près de maman. Les pieds restent près. Les mains restent tenues.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1469,6 +1492,11 @@
       <c r="AV3" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>narrateur|Hadrien est au marché. Que fait-il ?</t>
         </is>
       </c>
     </row>
@@ -1641,6 +1669,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>narrateur|Hadrien reste avec maman. L'accompagnant est là. La main est tenue. Les pieds restent près.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1803,6 +1836,11 @@
         <v>8</v>
       </c>
       <c r="AV5" s="2" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>narrateur|Hadrien et maman rentrent avec les fleurs. Ils marchent ensemble.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1965,6 +2003,11 @@
         <v>8</v>
       </c>
       <c r="AV6" s="2" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -1983,7 +2026,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:A3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2000,6 +2043,13 @@
       <c r="A2" t="inlineStr">
         <is>
           <t>conversion structurelle, prompts de choix alignés, TTS profilé</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-SEC.ADU.002-07.xlsx
+++ b/stories/arbres/ATOM-SEC.ADU.002-07.xlsx
@@ -844,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW6"/>
+  <dimension ref="A1:AX6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1143,6 +1143,11 @@
           <t>script</t>
         </is>
       </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1312,6 +1317,7 @@
 narrateur|Hadrien hoche la tête. Il sent la main de maman. La main est chaude. Ils sentent les roses. Hadrien reste avec maman. L'adulte connu est là. Hadrien est calme. Il sourit. Maman prend un bouquet. Hadrien reste à côté. Rester avec l'accompagnant, c'est rester près de maman. Les pieds restent près. Les mains restent tenues.</t>
         </is>
       </c>
+      <c r="AX2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1499,6 +1505,7 @@
           <t>narrateur|Hadrien est au marché. Que fait-il ?</t>
         </is>
       </c>
+      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1674,6 +1681,7 @@
           <t>narrateur|Hadrien reste avec maman. L'accompagnant est là. La main est tenue. Les pieds restent près.</t>
         </is>
       </c>
+      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1841,6 +1849,7 @@
           <t>narrateur|Hadrien et maman rentrent avec les fleurs. Ils marchent ensemble.</t>
         </is>
       </c>
+      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -2008,6 +2017,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX6" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2026,7 +2036,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2050,6 +2060,20 @@
       <c r="A3" t="inlineStr">
         <is>
           <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
         </is>
       </c>
     </row>
@@ -2064,7 +2088,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -2251,6 +2275,18 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ids de bruits (vide = silence). Le bruit se joue, puis l'histoire reprend au calme.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/stories/arbres/ATOM-SEC.ADU.002-07.xlsx
+++ b/stories/arbres/ATOM-SEC.ADU.002-07.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B30"/>
+  <dimension ref="A1:B31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -544,7 +544,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Hadrien reste avec maman au marché</t>
+          <t>Le pétale collé à la chaussure</t>
         </is>
       </c>
     </row>
@@ -830,6 +830,18 @@
       <c r="B30" t="inlineStr">
         <is>
           <t>voix-roles-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>fil_rouge</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>L'eau clapote dans un seau. Un pétale rose colle à la chaussure. Raphaël reste avec l'accompagnant, près des tulipes.</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1184,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Hadrien va au marché aux fleurs. Maman vient avec lui. Maman est l'accompagnant. Hadrien aime rester avec l'accompagnant. Il marche à côté de maman. Ses pieds restent près des pieds de maman. Maman tient sa main. Les mains restent dans la main de maman. Ils voient des tulipes. Hadrien reste près. Tu restes avec moi. Hadrien hoche la tête. Il sent la main de maman. La main est chaude. Ils sentent les roses. Hadrien reste avec maman. L'adulte connu est là. Hadrien est calme. Il sourit. Maman prend un bouquet. Hadrien reste à côté. Rester avec l'accompagnant, c'est rester près de maman. Les pieds restent près. Les mains restent tenues.</t>
+          <t>L'eau clapote dans un seau vert. Les tiges trempent, toutes droites. Un pétale rose colle à une chaussure. Il est tout mouillé, tout léger. Le pavé brille, encore humide. Ça sent les roses, tout fort. Une tulipe rouge penche un peu. Raphaël vit ici, avec maman. Maman, l'eau clapote ! Oui. Les fleurs boivent. Tu vois le pétale, sur ta chaussure ? Oui. Il est rose. En ce moment, ils marchent entre les seaux. Maman tient la main de Raphaël. La main est chaude. Les pieds de Raphaël restent près. Maman est l'accompagnant. Raphaël aime rester avec l'accompagnant. Tu restes avec moi ? Oui, maman. Bravo. Tu restes avec l'adulte connu. Ils voient des tulipes. Les tulipes sont rouges et jaunes. Une feuille lisse touche le seau. Elles sont droites ! Oui. Toutes droites, dans l'eau. Maman choisit un bouquet. Raphaël reste à côté. Ses pieds restent près des pieds de maman. Les mains restent dans la main de maman. Tu restes bien près. Tu as fait du bon travail. Ils sentent les roses. L'odeur est douce, un peu sucrée. Ça sent bon ! Oui. Ça sent les roses. Raphaël reste avec maman. L'adulte connu reste près. Je reste avec l'accompagnant. Oui. Bravo, Raphaël. Maman prend le bouquet. Le papier autour fait un petit bruit. Raphaël reste à côté. On rentre ensemble ? Oui. Ils marchent vers la maison. Le pétale voyage encore sur la chaussure. Le pavé fait un bruit mouillé. Tu tiens encore ma main ? Oui, maman. Bravo. Parce qu'il reste près, c'est simple. Rester avec l'accompagnant, c'est rester près. Raphaël est calme. Le bouquet penche un peu. Les pieds restent près. Oui. Le seau vert clapote encore, derrière eux.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1312,12 +1324,77 @@
       <c r="AV2" s="2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>narrateur|Hadrien va au marché aux fleurs. Maman vient avec lui. Maman est l'accompagnant. Hadrien aime rester avec l'accompagnant. Il marche à côté de maman. Ses pieds restent près des pieds de maman. Maman tient sa main. Les mains restent dans la main de maman. Ils voient des tulipes. Hadrien reste près.
-maman|Tu restes avec moi.
-narrateur|Hadrien hoche la tête. Il sent la main de maman. La main est chaude. Ils sentent les roses. Hadrien reste avec maman. L'adulte connu est là. Hadrien est calme. Il sourit. Maman prend un bouquet. Hadrien reste à côté. Rester avec l'accompagnant, c'est rester près de maman. Les pieds restent près. Les mains restent tenues.</t>
-        </is>
-      </c>
-      <c r="AX2" t="inlineStr"/>
+          <t>narrateur|L'eau clapote dans un seau vert.
+narrateur|Les tiges trempent, toutes droites.
+narrateur|Un pétale rose colle à une chaussure.
+narrateur|Il est tout mouillé, tout léger.
+narrateur|Le pavé brille, encore humide.
+narrateur|Ça sent les roses, tout fort.
+narrateur|Une tulipe rouge penche un peu.
+narrateur|Raphaël vit ici, avec maman.
+enfant-m|Maman, l'eau clapote !
+maman|Oui.
+maman|Les fleurs boivent.
+maman|Tu vois le pétale, sur ta chaussure ?
+enfant-m|Oui.
+enfant-m|Il est rose.
+narrateur|En ce moment, ils marchent entre les seaux.
+narrateur|Maman tient la main de Raphaël.
+narrateur|La main est chaude.
+narrateur|Les pieds de Raphaël restent près.
+narrateur|Maman est l'accompagnant.
+narrateur|Raphaël aime rester avec l'accompagnant.
+maman|Tu restes avec moi ?
+enfant-m|Oui, maman.
+maman|Bravo.
+maman|Tu restes avec l'adulte connu.
+narrateur|Ils voient des tulipes.
+narrateur|Les tulipes sont rouges et jaunes.
+narrateur|Une feuille lisse touche le seau.
+enfant-m|Elles sont droites !
+maman|Oui.
+maman|Toutes droites, dans l'eau.
+narrateur|Maman choisit un bouquet.
+narrateur|Raphaël reste à côté.
+narrateur|Ses pieds restent près des pieds de maman.
+narrateur|Les mains restent dans la main de maman.
+maman|Tu restes bien près.
+maman|Tu as fait du bon travail.
+narrateur|Ils sentent les roses.
+narrateur|L'odeur est douce, un peu sucrée.
+enfant-m|Ça sent bon !
+maman|Oui.
+maman|Ça sent les roses.
+narrateur|Raphaël reste avec maman.
+narrateur|L'adulte connu reste près.
+enfant-m|Je reste avec l'accompagnant.
+maman|Oui.
+maman|Bravo, Raphaël.
+narrateur|Maman prend le bouquet.
+narrateur|Le papier autour fait un petit bruit.
+narrateur|Raphaël reste à côté.
+maman|On rentre ensemble ?
+enfant-m|Oui.
+narrateur|Ils marchent vers la maison.
+narrateur|Le pétale voyage encore sur la chaussure.
+narrateur|Le pavé fait un bruit mouillé.
+maman|Tu tiens encore ma main ?
+enfant-m|Oui, maman.
+maman|Bravo.
+narrateur|Parce qu'il reste près, c'est simple.
+narrateur|Rester avec l'accompagnant, c'est rester près.
+narrateur|Raphaël est calme.
+narrateur|Le bouquet penche un peu.
+maman|Les pieds restent près.
+enfant-m|Oui.
+narrateur|Le seau vert clapote encore, derrière eux.</t>
+        </is>
+      </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>marche,fleurs</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1342,7 +1419,7 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Hadrien est au marché. Que fait-il ?</t>
+          <t>Raphaël est au marché. Que fait-il ?</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
@@ -1502,7 +1579,8 @@
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>narrateur|Hadrien est au marché. Que fait-il ?</t>
+          <t>narrateur|Raphaël est au marché.
+narrateur|Que fait-il ?</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr"/>
@@ -1530,7 +1608,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Hadrien reste avec maman. L'accompagnant est là. La main est tenue. Les pieds restent près.</t>
+          <t>Raphaël reste avec maman. Maman est l'accompagnant. La main est tenue. Les pieds restent près. Tu restes avec l'accompagnant ? Oui. Avec toi. Bravo, Raphaël. Tu restes avec l'adulte connu. Le bouquet sent encore les roses.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -1678,7 +1756,16 @@
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>narrateur|Hadrien reste avec maman. L'accompagnant est là. La main est tenue. Les pieds restent près.</t>
+          <t>narrateur|Raphaël reste avec maman.
+narrateur|Maman est l'accompagnant.
+narrateur|La main est tenue.
+narrateur|Les pieds restent près.
+maman|Tu restes avec l'accompagnant ?
+enfant-m|Oui.
+enfant-m|Avec toi.
+maman|Bravo, Raphaël.
+maman|Tu restes avec l'adulte connu.
+narrateur|Le bouquet sent encore les roses.</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr"/>
@@ -1706,7 +1793,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Hadrien et maman rentrent avec les fleurs. Ils marchent ensemble.</t>
+          <t>À la maison, le bouquet va dans l'eau. Tu as marché près de moi ? Oui, maman. Bravo. Tu as fait du bon travail. Raphaël enlève le pétale de sa chaussure. Il est encore un peu mouillé. Tu restes avec moi, au marché. Oui. Les tulipes se tiennent droites. L'eau de la carafe est calme.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -1846,7 +1933,17 @@
       <c r="AV5" s="2" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>narrateur|Hadrien et maman rentrent avec les fleurs. Ils marchent ensemble.</t>
+          <t>narrateur|À la maison, le bouquet va dans l'eau.
+maman|Tu as marché près de moi ?
+enfant-m|Oui, maman.
+maman|Bravo.
+maman|Tu as fait du bon travail.
+narrateur|Raphaël enlève le pétale de sa chaussure.
+narrateur|Il est encore un peu mouillé.
+maman|Tu restes avec moi, au marché.
+enfant-m|Oui.
+narrateur|Les tulipes se tiennent droites.
+narrateur|L'eau de la carafe est calme.</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr"/>
@@ -1874,7 +1971,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Je suis resté avec maman. Avec l'accompagnant. Bravo. C'est du bon travail. Le pétale sèche sur le rebord. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -2014,7 +2111,12 @@
       <c r="AV6" s="2" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-m|Je suis resté avec maman.
+maman|Avec l'accompagnant.
+maman|Bravo.
+maman|C'est du bon travail.
+narrateur|Le pétale sèche sur le rebord.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr"/>
@@ -2036,7 +2138,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:A6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2074,6 +2176,13 @@
       <c r="A5" t="inlineStr">
         <is>
           <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>F-NAR-009 ouverture du monde, fusion agents</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-SEC.ADU.002-07.xlsx
+++ b/stories/arbres/ATOM-SEC.ADU.002-07.xlsx
@@ -1184,12 +1184,12 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>L'eau clapote dans un seau vert. Les tiges trempent, toutes droites. Un pétale rose colle à une chaussure. Il est tout mouillé, tout léger. Le pavé brille, encore humide. Ça sent les roses, tout fort. Une tulipe rouge penche un peu. Raphaël vit ici, avec maman. Maman, l'eau clapote ! Oui. Les fleurs boivent. Tu vois le pétale, sur ta chaussure ? Oui. Il est rose. En ce moment, ils marchent entre les seaux. Maman tient la main de Raphaël. La main est chaude. Les pieds de Raphaël restent près. Maman est l'accompagnant. Raphaël aime rester avec l'accompagnant. Tu restes avec moi ? Oui, maman. Bravo. Tu restes avec l'adulte connu. Ils voient des tulipes. Les tulipes sont rouges et jaunes. Une feuille lisse touche le seau. Elles sont droites ! Oui. Toutes droites, dans l'eau. Maman choisit un bouquet. Raphaël reste à côté. Ses pieds restent près des pieds de maman. Les mains restent dans la main de maman. Tu restes bien près. Tu as fait du bon travail. Ils sentent les roses. L'odeur est douce, un peu sucrée. Ça sent bon ! Oui. Ça sent les roses. Raphaël reste avec maman. L'adulte connu reste près. Je reste avec l'accompagnant. Oui. Bravo, Raphaël. Maman prend le bouquet. Le papier autour fait un petit bruit. Raphaël reste à côté. On rentre ensemble ? Oui. Ils marchent vers la maison. Le pétale voyage encore sur la chaussure. Le pavé fait un bruit mouillé. Tu tiens encore ma main ? Oui, maman. Bravo. Parce qu'il reste près, c'est simple. Rester avec l'accompagnant, c'est rester près. Raphaël est calme. Le bouquet penche un peu. Les pieds restent près. Oui. Le seau vert clapote encore, derrière eux.</t>
+          <t>L'eau clapote dans un seau vert. Les tiges trempent, toutes droites. Un pétale rose colle à une chaussure. Il est tout mouillé, tout léger. Le pavé brille, encore humide. Ça sent les roses, tout fort. Une tulipe rouge penche un peu. Raphaël vit ici, avec maman. Maman, l'eau clapote ! Oui. Les fleurs boivent. Tu vois le pétale, sur ta chaussure ? Oui. Il est rose. En ce moment, ils marchent entre les seaux. Maman tient la main de Raphaël. La main est chaude. Les pieds de Raphaël restent près. Maman est l'accompagnant. Raphaël aime rester avec l'accompagnant. Tu restes avec moi ? Oui, maman. Bravo. Tu restes avec l'adulte connu. Ils voient des tulipes. Les tulipes sont rouges et jaunes. Une feuille lisse touche le seau. Elles sont droites ! Oui. Toutes droites, dans l'eau. Maman choisit un bouquet. Raphaël reste à côté. Ses pieds restent près des pieds de maman. Les mains restent dans la main de maman. Tu restes bien près. Ils sentent les roses. L'odeur est douce, un peu sucrée. Ça sent bon ! Oui. Ça sent les roses. Raphaël reste avec maman. L'adulte connu reste près. Je reste avec l'accompagnant. Oui. Bravo, Raphaël. Maman prend le bouquet. Le papier autour fait un petit bruit. Raphaël reste à côté. On rentre ensemble ? Oui. Ils marchent vers la maison. Le pétale voyage encore sur la chaussure. Le pavé fait un bruit mouillé. Tu tiens encore ma main ? Oui, maman. Bravo. Parce qu'il reste près, c'est simple. Rester avec l'accompagnant, c'est rester près. Raphaël est calme. Le bouquet penche un peu. Les pieds restent près. Oui. Le seau vert clapote encore, derrière eux.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Hadrien va au marché aux fleurs. Maman vient avec lui. Maman est l'accompagnant. Hadrien aime &lt;emphasis level="moderate"&gt;rester&lt;/emphasis&gt; avec l'accompagnant. Il marche à côté de maman. Ses pieds restent près des pieds de maman. Maman tient sa main. Les mains restent dans la main de maman. Ils voient des tulipes. Hadrien reste près. Maman dit : tu restes avec moi. Hadrien hoche la tête. Il sent la main de maman. La main est chaude. Ils sentent les roses. Hadrien reste avec maman. L'adulte connu est là. Hadrien est calme. Il sourit. Maman prend un bouquet. Hadrien reste à côté. Rester avec l'accompagnant, c'est rester près de maman. Les pieds restent près. Les mains restent tenues.&lt;/prosody&gt;&lt;break time="400ms"/&gt;&lt;/speak&gt;</t>
+          <t>L'eau clapote dans un seau vert. Les tiges trempent, toutes droites. Un pétale rose colle à une chaussure. Il est tout mouillé, tout léger. Le pavé brille, encore humide. Ça sent les roses, tout fort. Une tulipe rouge penche un peu. Raphaël vit ici, avec maman. Maman, l'eau clapote ! Oui. Les fleurs boivent. Tu vois le pétale, sur ta chaussure ? Oui. Il est rose. En ce moment, ils marchent entre les seaux. Maman tient la main de Raphaël. La main est chaude. Les pieds de Raphaël restent près. Maman est l'accompagnant. Raphaël aime rester avec l'accompagnant. Tu restes avec moi ? Oui, maman. Bravo. Tu restes avec l'adulte connu. Ils voient des tulipes. Les tulipes sont rouges et jaunes. Une feuille lisse touche le seau. Elles sont droites ! Oui. Toutes droites, dans l'eau. Maman choisit un bouquet. Raphaël reste à côté. Ses pieds restent près des pieds de maman. Les mains restent dans la main de maman. Tu restes bien près. Ils sentent les roses. L'odeur est douce, un peu sucrée. Ça sent bon ! Oui. Ça sent les roses. Raphaël reste avec maman. L'adulte connu reste près. Je reste avec l'accompagnant. Oui. Bravo, Raphaël. Maman prend le bouquet. Le papier autour fait un petit bruit. Raphaël reste à côté. On rentre ensemble ? Oui. Ils marchent vers la maison. Le pétale voyage encore sur la chaussure. Le pavé fait un bruit mouillé. Tu tiens encore ma main ? Oui, maman. Bravo. Parce qu'il reste près, c'est simple. Rester avec l'accompagnant, c'est rester près. Raphaël est calme. Le bouquet penche un peu. Les pieds restent près. Oui. Le seau vert clapote encore, derrière eux.</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -1359,7 +1359,6 @@
 narrateur|Ses pieds restent près des pieds de maman.
 narrateur|Les mains restent dans la main de maman.
 maman|Tu restes bien près.
-maman|Tu as fait du bon travail.
 narrateur|Ils sentent les roses.
 narrateur|L'odeur est douce, un peu sucrée.
 enfant-m|Ça sent bon !
@@ -1424,7 +1423,7 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="low"&gt;Hadrien est au marché. Que fait-il ?&lt;/prosody&gt;&lt;break time="250ms"/&gt;&lt;/speak&gt;</t>
+          <t>Raphaël est au marché. Que fait-il ?</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
@@ -1583,7 +1582,6 @@
 narrateur|Que fait-il ?</t>
         </is>
       </c>
-      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1613,7 +1611,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="low"&gt;Hadrien reste avec maman. L'accompagnant est là. La &lt;emphasis level="moderate"&gt;main&lt;/emphasis&gt; est tenue. Les pieds restent près.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Raphaël reste avec maman. Maman est l'accompagnant. La main est tenue. Les pieds restent près. Tu restes avec l'accompagnant ? Oui. Avec toi. Bravo, Raphaël. Tu restes avec l'adulte connu. Le bouquet sent encore les roses.</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -1768,7 +1766,6 @@
 narrateur|Le bouquet sent encore les roses.</t>
         </is>
       </c>
-      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1793,12 +1790,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>À la maison, le bouquet va dans l'eau. Tu as marché près de moi ? Oui, maman. Bravo. Tu as fait du bon travail. Raphaël enlève le pétale de sa chaussure. Il est encore un peu mouillé. Tu restes avec moi, au marché. Oui. Les tulipes se tiennent droites. L'eau de la carafe est calme.</t>
+          <t>À la maison, le bouquet va dans l'eau. Tu as marché près de moi ? Oui, maman. Bravo. Raphaël enlève le pétale de sa chaussure. Il est encore un peu mouillé. Tu restes avec moi, au marché. Oui. Les tulipes se tiennent droites. L'eau de la carafe est calme.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="low"&gt;Hadrien et maman rentrent avec les fleurs. Ils marchent ensemble.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>À la maison, le bouquet va dans l'eau. Tu as marché près de moi ? Oui, maman. Bravo. Raphaël enlève le pétale de sa chaussure. Il est encore un peu mouillé. Tu restes avec moi, au marché. Oui. Les tulipes se tiennent droites. L'eau de la carafe est calme.</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1937,7 +1934,6 @@
 maman|Tu as marché près de moi ?
 enfant-m|Oui, maman.
 maman|Bravo.
-maman|Tu as fait du bon travail.
 narrateur|Raphaël enlève le pétale de sa chaussure.
 narrateur|Il est encore un peu mouillé.
 maman|Tu restes avec moi, au marché.
@@ -1946,7 +1942,6 @@
 narrateur|L'eau de la carafe est calme.</t>
         </is>
       </c>
-      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1971,12 +1966,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>Je suis resté avec maman. Avec l'accompagnant. Bravo. C'est du bon travail. Le pétale sèche sur le rebord. L'histoire est finie.</t>
+          <t>Je suis resté avec maman. Avec l'accompagnant. Bravo. Le pétale sèche sur le rebord.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="low"&gt;L'histoire est finie.&lt;/prosody&gt;&lt;break time="600ms"/&gt;&lt;/speak&gt;</t>
+          <t>Je suis resté avec maman. Avec l'accompagnant. Bravo. Le pétale sèche sur le rebord.</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -2114,12 +2109,9 @@
           <t>enfant-m|Je suis resté avec maman.
 maman|Avec l'accompagnant.
 maman|Bravo.
-maman|C'est du bon travail.
-narrateur|Le pétale sèche sur le rebord.
-narrateur|L'histoire est finie.</t>
-        </is>
-      </c>
-      <c r="AX6" t="inlineStr"/>
+narrateur|Le pétale sèche sur le rebord.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2138,7 +2130,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A6"/>
+  <dimension ref="A1:A7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2183,6 +2175,13 @@
       <c r="A6" t="inlineStr">
         <is>
           <t>F-NAR-009 ouverture du monde, fusion agents</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>F-NAR-008 récit, pas une leçon en puces</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-SEC.ADU.002-07.xlsx
+++ b/stories/arbres/ATOM-SEC.ADU.002-07.xlsx
@@ -671,7 +671,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>marché aux fleurs</t>
+          <t>marché aux fleurs, seaux, tulipes et roses</t>
         </is>
       </c>
     </row>
@@ -683,7 +683,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Hadrien, maman</t>
+          <t>Raphaël, maman</t>
         </is>
       </c>
     </row>
